--- a/모의고사/코코모의고사2회_정답.xlsx
+++ b/모의고사/코코모의고사2회_정답.xlsx
@@ -93,7 +93,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
